--- a/templates/GCPS_DMF_026.5_A-EDesign and Specification QC Form.xlsx
+++ b/templates/GCPS_DMF_026.5_A-EDesign and Specification QC Form.xlsx
@@ -1120,11 +1120,11 @@
   <ns0:pageMargins left="0.70866141732283472" right="0.70866141732283472" top="1.2598425196850394" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <ns0:pageSetup paperSize="9" orientation="landscape" ns4:id="rId1"/>
   <ns0:headerFooter>
-    <ns0:oddHeader>&amp;L&amp;G&amp;C&amp;"Arial"&amp;16Design and Specification QC Form
+    <ns0:oddHeader>&amp;L&amp;"Arial"&amp;10Study Code: &lt;Code&gt;
+System: QCTMS LC&amp;C&amp;"Arial"&amp;16Design and Specification QC Form
 &amp;"Arial"&amp;14QCTMS LC
 &amp;"Arial"&amp;11Version No.: &lt;X.X&gt;
-&amp;"Arial"&amp;11Version Date: &lt;DD/MMM/YYYY&gt;&amp;R&amp;"Arial"&amp;10Study Code: &lt;Code&gt;
-System: QCTMS LC</ns0:oddHeader>
+&amp;"Arial"&amp;11Version Date: &lt;DD/MMM/YYYY&gt;&amp;R&amp;G</ns0:oddHeader>
     <ns0:oddFooter>&amp;L&amp;"Arial,Standard"GCPS_DMF_026.5_A&amp;C&amp;"Arial,Standard"Effective Date: 16/DEC/2024&amp;R&amp;"Arial,Standard"Page &amp;P of &amp;N</ns0:oddFooter>
   </ns0:headerFooter>
   <ns0:legacyDrawingHF ns4:id="rId2"/>
@@ -1269,11 +1269,11 @@
   <ns0:pageMargins left="0.70866141732283472" right="0.70866141732283472" top="1.2598425196850394" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <ns0:pageSetup paperSize="9" orientation="landscape" ns4:id="rId1"/>
   <ns0:headerFooter>
-    <ns0:oddHeader>&amp;L&amp;G&amp;C&amp;"Arial"&amp;16Design and Specification QC Form
+    <ns0:oddHeader>&amp;L&amp;"Arial"&amp;10Study Code: &lt;Code&gt;
+System: &lt;System&gt;&amp;C&amp;"Arial"&amp;16Design and Specification QC Form
 &amp;"Arial"&amp;14New
 &amp;"Arial"&amp;11Version No.: &lt;X.X&gt;
-&amp;"Arial"&amp;11Version Date: &lt;DD/MMM/YYYY&gt;&amp;R&amp;"Arial"&amp;10Study Code: &lt;Code&gt;
-System: &lt;System&gt;</ns0:oddHeader>
+&amp;"Arial"&amp;11Version Date: &lt;DD/MMM/YYYY&gt;&amp;R&amp;G</ns0:oddHeader>
     <ns0:oddFooter>&amp;L&amp;"Arial,Standard"GCPS_DMF_026.5_E&amp;C&amp;"Arial,Standard"Effective Date: 16/DEC/2024&amp;R&amp;"Arial,Standard"Page &amp;P of &amp;N</ns0:oddFooter>
   </ns0:headerFooter>
   <ns0:legacyDrawingHF ns4:id="rId2"/>
@@ -1386,11 +1386,11 @@
   <ns0:pageMargins left="0.7" right="0.7" top="1.2604166666666667" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <ns0:pageSetup paperSize="9" orientation="landscape" ns4:id="rId1"/>
   <ns0:headerFooter>
-    <ns0:oddHeader>&amp;L&amp;G&amp;C&amp;"Arial"&amp;16Design and Specification QC Form
+    <ns0:oddHeader>&amp;L&amp;"Arial"&amp;10Study Code: &lt;Code&gt;
+System: QCTMS ePRO&amp;C&amp;"Arial"&amp;16Design and Specification QC Form
 &amp;"Arial"&amp;14QCTMS ePRO
 &amp;"Arial"&amp;11Version No.: &lt;X.X&gt;
-&amp;"Arial"&amp;11Version Date: &lt;DD/MMM/YYYY&gt;&amp;R&amp;"Arial"&amp;10Study Code: &lt;Code&gt;
-System: QCTMS ePRO</ns0:oddHeader>
+&amp;"Arial"&amp;11Version Date: &lt;DD/MMM/YYYY&gt;&amp;R&amp;G</ns0:oddHeader>
     <ns0:oddFooter>&amp;L&amp;"Arial,Standard"GCPS_DMF_026.5_B&amp;C&amp;"Arial,Standard"Effective Date: 16/DEC/2024&amp;R&amp;"Arial,Standard"Page &amp;P of &amp;N</ns0:oddFooter>
   </ns0:headerFooter>
   <ns0:legacyDrawingHF ns4:id="rId2"/>
@@ -1627,11 +1627,11 @@
   <ns0:pageMargins left="0.70866141732283472" right="0.70866141732283472" top="1.2598425196850394" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <ns0:pageSetup paperSize="9" orientation="landscape" ns4:id="rId1"/>
   <ns0:headerFooter>
-    <ns0:oddHeader>&amp;L&amp;G&amp;C&amp;"Arial"&amp;16Design and Specification QC Form
+    <ns0:oddHeader>&amp;L&amp;"Arial"&amp;10Study Code: &lt;Code&gt;
+System: Viedoc&amp;C&amp;"Arial"&amp;16Design and Specification QC Form
 &amp;"Arial"&amp;14Items and Groups
 &amp;"Arial"&amp;11Version No.: &lt;X.X&gt;
-&amp;"Arial"&amp;11Version Date: &lt;DD/MMM/YYYY&gt;&amp;R&amp;"Arial"&amp;10Study Code: &lt;Code&gt;
-System: Viedoc</ns0:oddHeader>
+&amp;"Arial"&amp;11Version Date: &lt;DD/MMM/YYYY&gt;&amp;R&amp;G</ns0:oddHeader>
     <ns0:oddFooter>&amp;L&amp;"Arial,Standard"GCPS_DMF_026.4_C1&amp;C&amp;"Arial,Standard"Effective Date: 16/DEC/2024&amp;R&amp;"Arial,Standard"Page &amp;P of &amp;N</ns0:oddFooter>
   </ns0:headerFooter>
   <ns0:legacyDrawingHF ns4:id="rId2"/>
@@ -1751,11 +1751,11 @@
   <ns0:pageMargins left="0.70866141732283472" right="0.70866141732283472" top="1.2598425196850394" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <ns0:pageSetup paperSize="9" orientation="landscape" ns4:id="rId1"/>
   <ns0:headerFooter>
-    <ns0:oddHeader>&amp;L&amp;G&amp;C&amp;"Arial"&amp;16Design and Specification QC Form
+    <ns0:oddHeader>&amp;L&amp;"Arial"&amp;10Study Code: &lt;Code&gt;
+System: Viedoc&amp;C&amp;"Arial"&amp;16Design and Specification QC Form
 &amp;"Arial"&amp;14Study Workflow - Events
 &amp;"Arial"&amp;11Version No.: &lt;X.X&gt;
-&amp;"Arial"&amp;11Version Date: &lt;DD/MMM/YYYY&gt;&amp;R&amp;"Arial"&amp;10Study Code: &lt;Code&gt;
-System: Viedoc</ns0:oddHeader>
+&amp;"Arial"&amp;11Version Date: &lt;DD/MMM/YYYY&gt;&amp;R&amp;G</ns0:oddHeader>
     <ns0:oddFooter>&amp;L&amp;"Arial,Standard"GCPS_DMF_026.4_C2&amp;C&amp;"Arial,Standard"Effective Date: 16/DEC/2024&amp;R&amp;"Arial,Standard"Page &amp;P of &amp;N</ns0:oddFooter>
   </ns0:headerFooter>
   <ns0:legacyDrawingHF ns4:id="rId2"/>
@@ -1832,11 +1832,11 @@
   <ns0:pageMargins left="0.70866141732283472" right="0.70866141732283472" top="1.2598425196850394" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <ns0:pageSetup paperSize="9" orientation="landscape" ns4:id="rId1"/>
   <ns0:headerFooter>
-    <ns0:oddHeader>&amp;L&amp;G&amp;C&amp;"Arial"&amp;16Design and Specification QC Form
+    <ns0:oddHeader>&amp;L&amp;"Arial"&amp;10Study Code: &lt;Code&gt;
+System: Viedoc&amp;C&amp;"Arial"&amp;16Design and Specification QC Form
 &amp;"Arial"&amp;14Study Workflow - Activities
 &amp;"Arial"&amp;11Version No.: &lt;X.X&gt;
-&amp;"Arial"&amp;11Version Date: &lt;DD/MMM/YYYY&gt;&amp;R&amp;"Arial"&amp;10Study Code: &lt;Code&gt;
-System: Viedoc</ns0:oddHeader>
+&amp;"Arial"&amp;11Version Date: &lt;DD/MMM/YYYY&gt;&amp;R&amp;G</ns0:oddHeader>
     <ns0:oddFooter>&amp;L&amp;"Arial,Standard"GCPS_DMF_026.4_C3&amp;C&amp;"Arial,Standard"Effective Date: 16/DEC/2024&amp;R&amp;"Arial,Standard"Page &amp;P of &amp;N</ns0:oddFooter>
   </ns0:headerFooter>
   <ns0:legacyDrawingHF ns4:id="rId2"/>
@@ -1907,11 +1907,11 @@
   <ns0:pageMargins left="0.70866141732283472" right="0.70866141732283472" top="1.2598425196850394" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <ns0:pageSetup paperSize="9" orientation="landscape" ns4:id="rId1"/>
   <ns0:headerFooter>
-    <ns0:oddHeader>&amp;L&amp;G&amp;C&amp;"Arial"&amp;16Design and Specification QC Form
+    <ns0:oddHeader>&amp;L&amp;"Arial"&amp;10Study Code: &lt;Code&gt;
+System: Viedoc&amp;C&amp;"Arial"&amp;16Design and Specification QC Form
 &amp;"Arial"&amp;14Study Workflow - Forms
 &amp;"Arial"&amp;11Version No.: &lt;X.X&gt;
-&amp;"Arial"&amp;11Version Date: &lt;DD/MMM/YYYY&gt;&amp;R&amp;"Arial"&amp;10Study Code: &lt;Code&gt;
-System: Viedoc</ns0:oddHeader>
+&amp;"Arial"&amp;11Version Date: &lt;DD/MMM/YYYY&gt;&amp;R&amp;G</ns0:oddHeader>
     <ns0:oddFooter>&amp;L&amp;"Arial,Standard"GCPS_DMF_026.4_C4&amp;C&amp;"Arial,Standard"Effective Date: 16/DEC/2024&amp;R&amp;"Arial,Standard"Page &amp;P of &amp;N</ns0:oddFooter>
   </ns0:headerFooter>
   <ns0:legacyDrawingHF ns4:id="rId2"/>
@@ -1985,11 +1985,11 @@
   <ns0:pageMargins left="0.70866141732283472" right="0.70866141732283472" top="1.2598425196850394" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <ns0:pageSetup paperSize="9" orientation="landscape" ns4:id="rId1"/>
   <ns0:headerFooter>
-    <ns0:oddHeader>&amp;L&amp;G&amp;C&amp;"Arial"&amp;16Design and Specification QC Form
+    <ns0:oddHeader>&amp;L&amp;"Arial"&amp;10Study Code: &lt;Code&gt;
+System: Viedoc&amp;C&amp;"Arial"&amp;16Design and Specification QC Form
 &amp;"Arial"&amp;14Functions and Conditions
 &amp;"Arial"&amp;11Version No.: &lt;X.X&gt;
-&amp;"Arial"&amp;11Version Date: &lt;DD/MMM/YYYY&gt;&amp;R&amp;"Arial"&amp;10Study Code: &lt;Code&gt;
-System: Viedoc</ns0:oddHeader>
+&amp;"Arial"&amp;11Version Date: &lt;DD/MMM/YYYY&gt;&amp;R&amp;G</ns0:oddHeader>
     <ns0:oddFooter>&amp;L&amp;"Arial,Standard"GCPS_DMF_026.4_C5&amp;C&amp;"Arial,Standard"Effective Date: 16/DEC/2024&amp;R&amp;"Arial,Standard"Page &amp;P of &amp;N</ns0:oddFooter>
   </ns0:headerFooter>
   <ns0:legacyDrawingHF ns4:id="rId2"/>
@@ -2051,11 +2051,11 @@
   <ns0:pageMargins left="0.70866141732283472" right="0.70866141732283472" top="1.2598425196850394" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <ns0:pageSetup paperSize="9" orientation="landscape" ns4:id="rId1"/>
   <ns0:headerFooter>
-    <ns0:oddHeader>&amp;L&amp;G&amp;C&amp;"Arial"&amp;16Design and Specification QC Form
+    <ns0:oddHeader>&amp;L&amp;"Arial"&amp;10Study Code: &lt;Code&gt;
+System: Viedoc&amp;C&amp;"Arial"&amp;16Design and Specification QC Form
 &amp;"Arial"&amp;14Code lists
 &amp;"Arial"&amp;11Version No.: &lt;X.X&gt;
-&amp;"Arial"&amp;11Version Date: &lt;DD/MMM/YYYY&gt;&amp;R&amp;"Arial"&amp;10Study Code: &lt;Code&gt;
-System: Viedoc</ns0:oddHeader>
+&amp;"Arial"&amp;11Version Date: &lt;DD/MMM/YYYY&gt;&amp;R&amp;G</ns0:oddHeader>
     <ns0:oddFooter>&amp;L&amp;"Arial,Standard"GCPS_DMF_026.4_C6&amp;C&amp;"Arial,Standard"Effective Date: 16/DEC/2024&amp;R&amp;"Arial,Standard"Page &amp;P of &amp;N</ns0:oddFooter>
   </ns0:headerFooter>
   <ns0:legacyDrawingHF ns4:id="rId2"/>
@@ -2177,11 +2177,11 @@
   <ns0:pageMargins left="0.70866141732283472" right="0.70866141732283472" top="1.2598425196850394" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <ns0:pageSetup paperSize="9" orientation="landscape" ns4:id="rId1"/>
   <ns0:headerFooter>
-    <ns0:oddHeader>&amp;L&amp;G&amp;C&amp;"Arial"&amp;16Design and Specification QC Form
+    <ns0:oddHeader>&amp;L&amp;"Arial"&amp;10Study Code: &lt;Code&gt;
+System: Castor&amp;C&amp;"Arial"&amp;16Design and Specification QC Form
 &amp;"Arial"&amp;14Castor
 &amp;"Arial"&amp;11Version No.: &lt;X.X&gt;
-&amp;"Arial"&amp;11Version Date: &lt;DD/MMM/YYYY&gt;&amp;R&amp;"Arial"&amp;10Study Code: &lt;Code&gt;
-System: Castor</ns0:oddHeader>
+&amp;"Arial"&amp;11Version Date: &lt;DD/MMM/YYYY&gt;&amp;R&amp;G</ns0:oddHeader>
     <ns0:oddFooter>&amp;L&amp;"Arial,Standard"GCPS_DMF_026.5_D&amp;C&amp;"Arial,Standard"Effective Date: 16/DEC/2024&amp;R&amp;"Arial,Standard"Page &amp;P of &amp;N</ns0:oddFooter>
   </ns0:headerFooter>
   <ns0:legacyDrawingHF ns4:id="rId2"/>
